--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -521,6 +521,9 @@
       <c r="C11" t="str">
         <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -579,7 +582,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010512121015105100</v>
+        <v>0105121210151051010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F12" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>839_洋牡丹洋葱_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>80_冰清玉洁_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>3</v>
+      </c>
+      <c r="C18" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -582,7 +662,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0105121210151051010</v>
+        <v>01051212101510510101510102510510100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -604,6 +604,9 @@
       <c r="C21" t="str">
         <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -662,7 +665,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051212101510510101510102510510100</v>
+        <v>010512121015105101015101025105101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -608,9 +608,87 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>41_拉丝白_Spider White_Gerbera L._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>44_拉丝粉_Spider Pink_Gerbera L._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>43_拉丝红_Spider Red_Gerbera L._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>70_朝霞mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>71_霜雪mini_Snowy_Gerbera L._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>46_拉丝橙_Spider orange_Gerbera L._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="C28" t="str" xml:space="preserve">
+        <v xml:space="preserve">448_吊米 绿_hanging amaranthus
+green_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>543_柔丽思红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>100_绣球白_Hydrangea White S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F30" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -665,7 +743,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010512121015105101015101025105101010</v>
+        <v>01051212101510510101510102510510101010101010101055300</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -685,6 +685,9 @@
       <c r="A31" t="str">
         <v>4</v>
       </c>
+      <c r="C31" t="str">
+        <v>388_大丽花_dahlia_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -688,6 +688,9 @@
       <c r="C31" t="str">
         <v>388_大丽花_dahlia_undefined_1bunch</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -746,7 +749,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051212101510510101510102510510101010101010101055300</v>
+        <v>01051212101510510101510102510510101010101010101055301</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-9-24.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -689,12 +689,20 @@
         <v>388_大丽花_dahlia_undefined_1bunch</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>82_非洲菊绿 绿扣子_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L32"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -749,7 +757,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01051212101510510101510102510510101010101010101055301</v>
+        <v>01051212101510510101510102510510101010101010101055301010</v>
       </c>
     </row>
   </sheetData>
